--- a/Python/dz2/work/output/volunteer_workload.xlsx
+++ b/Python/dz2/work/output/volunteer_workload.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="77">
   <si>
     <t>task_date</t>
   </si>
@@ -37,19 +37,214 @@
     <t>comment</t>
   </si>
   <si>
+    <t>Кузнецов Дмитрий</t>
+  </si>
+  <si>
+    <t>Федорова Ольга</t>
+  </si>
+  <si>
+    <t>Громов Максим</t>
+  </si>
+  <si>
+    <t>Соколова Мария</t>
+  </si>
+  <si>
+    <t>Морозов Артем</t>
+  </si>
+  <si>
+    <t>Никитина Дарья</t>
+  </si>
+  <si>
+    <t>Орлова Елена</t>
+  </si>
+  <si>
+    <t>Алексеев Петр</t>
+  </si>
+  <si>
+    <t>Иванов Иван</t>
+  </si>
+  <si>
     <t>Петрова Анна</t>
   </si>
   <si>
+    <t>+7-900-555-55-55</t>
+  </si>
+  <si>
+    <t>+7-900-888-88-88</t>
+  </si>
+  <si>
+    <t>+7-901-222-22-22</t>
+  </si>
+  <si>
+    <t>+7-900-444-44-44</t>
+  </si>
+  <si>
+    <t>+7-900-777-77-77</t>
+  </si>
+  <si>
+    <t>+7-901-111-11-11</t>
+  </si>
+  <si>
+    <t>+7-900-666-66-66</t>
+  </si>
+  <si>
+    <t>+7-900-999-99-99</t>
+  </si>
+  <si>
+    <t>+7-900-111-11-11</t>
+  </si>
+  <si>
     <t>+7-900-222-22-22</t>
   </si>
   <si>
+    <t>Ася</t>
+  </si>
+  <si>
+    <t>Кира</t>
+  </si>
+  <si>
+    <t>Пират</t>
+  </si>
+  <si>
+    <t>Моника</t>
+  </si>
+  <si>
+    <t>Тиша</t>
+  </si>
+  <si>
+    <t>Луна</t>
+  </si>
+  <si>
+    <t>Боня</t>
+  </si>
+  <si>
+    <t>Бакс</t>
+  </si>
+  <si>
+    <t>Веста</t>
+  </si>
+  <si>
+    <t>Феликс</t>
+  </si>
+  <si>
+    <t>Сима</t>
+  </si>
+  <si>
+    <t>Граф</t>
+  </si>
+  <si>
+    <t>Лорд</t>
+  </si>
+  <si>
+    <t>Дина</t>
+  </si>
+  <si>
+    <t>Макс</t>
+  </si>
+  <si>
+    <t>Джек</t>
+  </si>
+  <si>
+    <t>Чарли</t>
+  </si>
+  <si>
+    <t>Мила</t>
+  </si>
+  <si>
+    <t>Лея</t>
+  </si>
+  <si>
     <t>Бим</t>
   </si>
   <si>
+    <t>Тайга</t>
+  </si>
+  <si>
+    <t>Том</t>
+  </si>
+  <si>
+    <t>Злата</t>
+  </si>
+  <si>
+    <t>Снежок</t>
+  </si>
+  <si>
+    <t>Рекс</t>
+  </si>
+  <si>
+    <t>Нора</t>
+  </si>
+  <si>
+    <t>Рыжик</t>
+  </si>
+  <si>
+    <t>Соня</t>
+  </si>
+  <si>
+    <t>Кузя</t>
+  </si>
+  <si>
+    <t>Рада</t>
+  </si>
+  <si>
+    <t>Марта</t>
+  </si>
+  <si>
+    <t>Оскар</t>
+  </si>
+  <si>
+    <t>Фрося</t>
+  </si>
+  <si>
+    <t>Арчи</t>
+  </si>
+  <si>
+    <t>Муся</t>
+  </si>
+  <si>
+    <t>Марс</t>
+  </si>
+  <si>
+    <t>Шерри</t>
+  </si>
+  <si>
+    <t>Спайк</t>
+  </si>
+  <si>
+    <t>Гера</t>
+  </si>
+  <si>
+    <t>Барсик</t>
+  </si>
+  <si>
+    <t>Кормление</t>
+  </si>
+  <si>
     <t>Лечение</t>
   </si>
   <si>
-    <t>Обработка кожи и контроль состояния</t>
+    <t>Социализация</t>
+  </si>
+  <si>
+    <t>Перевозка</t>
+  </si>
+  <si>
+    <t>Выгул</t>
+  </si>
+  <si>
+    <t>Кормление: плановая работа</t>
+  </si>
+  <si>
+    <t>Лечение: плановая работа</t>
+  </si>
+  <si>
+    <t>Социализация: плановая работа</t>
+  </si>
+  <si>
+    <t>Перевозка: плановая работа</t>
+  </si>
+  <si>
+    <t>Выгул: плановая работа</t>
   </si>
 </sst>
 </file>
@@ -411,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -439,25 +634,1589 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>46092</v>
+        <v>46083</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="2">
+        <v>46084</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3">
+        <v>40</v>
+      </c>
+      <c r="G3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4">
+        <v>50</v>
+      </c>
+      <c r="G4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2">
+        <v>46086</v>
+      </c>
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="F2">
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5">
+        <v>60</v>
+      </c>
+      <c r="G5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2">
+        <v>46087</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6">
+        <v>70</v>
+      </c>
+      <c r="G6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="2">
+        <v>46088</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7">
+        <v>80</v>
+      </c>
+      <c r="G7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="2">
+        <v>46090</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="2">
+        <v>46091</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9">
+        <v>40</v>
+      </c>
+      <c r="G9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="2">
+        <v>46092</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10">
+        <v>50</v>
+      </c>
+      <c r="G10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="2">
+        <v>46093</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11">
+        <v>60</v>
+      </c>
+      <c r="G11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="2">
+        <v>46094</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12">
+        <v>70</v>
+      </c>
+      <c r="G12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="2">
+        <v>46095</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13">
+        <v>80</v>
+      </c>
+      <c r="G13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="2">
+        <v>46097</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14">
+        <v>30</v>
+      </c>
+      <c r="G14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="2">
+        <v>46098</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15">
+        <v>40</v>
+      </c>
+      <c r="G15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="2">
+        <v>46099</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16">
+        <v>50</v>
+      </c>
+      <c r="G16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="2">
+        <v>46100</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17">
+        <v>60</v>
+      </c>
+      <c r="G17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="2">
+        <v>46101</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18">
+        <v>70</v>
+      </c>
+      <c r="G18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="2">
+        <v>46102</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19">
+        <v>80</v>
+      </c>
+      <c r="G19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="2">
+        <v>46104</v>
+      </c>
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" t="s">
         <v>45</v>
       </c>
-      <c r="G2" t="s">
+      <c r="E20" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20">
+        <v>30</v>
+      </c>
+      <c r="G20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="2">
+        <v>46105</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21">
+        <v>40</v>
+      </c>
+      <c r="G21" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="2">
+        <v>46106</v>
+      </c>
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22">
+        <v>50</v>
+      </c>
+      <c r="G22" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="2">
+        <v>46107</v>
+      </c>
+      <c r="B23" t="s">
         <v>11</v>
+      </c>
+      <c r="C23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" t="s">
+        <v>71</v>
+      </c>
+      <c r="F23">
+        <v>60</v>
+      </c>
+      <c r="G23" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="2">
+        <v>46108</v>
+      </c>
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24">
+        <v>70</v>
+      </c>
+      <c r="G24" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="2">
+        <v>46109</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" t="s">
+        <v>50</v>
+      </c>
+      <c r="E25" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25">
+        <v>80</v>
+      </c>
+      <c r="G25" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="2">
+        <v>46111</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26">
+        <v>30</v>
+      </c>
+      <c r="G26" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="2">
+        <v>46112</v>
+      </c>
+      <c r="B27" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" t="s">
+        <v>71</v>
+      </c>
+      <c r="F27">
+        <v>40</v>
+      </c>
+      <c r="G27" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28">
+        <v>50</v>
+      </c>
+      <c r="G28" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="2">
+        <v>46114</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" t="s">
+        <v>54</v>
+      </c>
+      <c r="E29" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29">
+        <v>60</v>
+      </c>
+      <c r="G29" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="2">
+        <v>46115</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" t="s">
+        <v>55</v>
+      </c>
+      <c r="E30" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30">
+        <v>70</v>
+      </c>
+      <c r="G30" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="2">
+        <v>46116</v>
+      </c>
+      <c r="B31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" t="s">
+        <v>56</v>
+      </c>
+      <c r="E31" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31">
+        <v>80</v>
+      </c>
+      <c r="G31" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B32" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" t="s">
+        <v>57</v>
+      </c>
+      <c r="E32" t="s">
+        <v>67</v>
+      </c>
+      <c r="F32">
+        <v>30</v>
+      </c>
+      <c r="G32" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="2">
+        <v>46119</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" t="s">
+        <v>58</v>
+      </c>
+      <c r="E33" t="s">
+        <v>68</v>
+      </c>
+      <c r="F33">
+        <v>40</v>
+      </c>
+      <c r="G33" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="2">
+        <v>46120</v>
+      </c>
+      <c r="B34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" t="s">
+        <v>59</v>
+      </c>
+      <c r="E34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F34">
+        <v>50</v>
+      </c>
+      <c r="G34" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="2">
+        <v>46121</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" t="s">
+        <v>60</v>
+      </c>
+      <c r="E35" t="s">
+        <v>70</v>
+      </c>
+      <c r="F35">
+        <v>60</v>
+      </c>
+      <c r="G35" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="2">
+        <v>46122</v>
+      </c>
+      <c r="B36" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" t="s">
+        <v>61</v>
+      </c>
+      <c r="E36" t="s">
+        <v>71</v>
+      </c>
+      <c r="F36">
+        <v>70</v>
+      </c>
+      <c r="G36" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="2">
+        <v>46123</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" t="s">
+        <v>27</v>
+      </c>
+      <c r="E37" t="s">
+        <v>67</v>
+      </c>
+      <c r="F37">
+        <v>80</v>
+      </c>
+      <c r="G37" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="2">
+        <v>46125</v>
+      </c>
+      <c r="B38" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" t="s">
+        <v>29</v>
+      </c>
+      <c r="E38" t="s">
+        <v>69</v>
+      </c>
+      <c r="F38">
+        <v>30</v>
+      </c>
+      <c r="G38" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" t="s">
+        <v>30</v>
+      </c>
+      <c r="E39" t="s">
+        <v>70</v>
+      </c>
+      <c r="F39">
+        <v>40</v>
+      </c>
+      <c r="G39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="2">
+        <v>46127</v>
+      </c>
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" t="s">
+        <v>71</v>
+      </c>
+      <c r="F40">
+        <v>50</v>
+      </c>
+      <c r="G40" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="2">
+        <v>46128</v>
+      </c>
+      <c r="B41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" t="s">
+        <v>67</v>
+      </c>
+      <c r="F41">
+        <v>60</v>
+      </c>
+      <c r="G41" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="2">
+        <v>46129</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" t="s">
+        <v>68</v>
+      </c>
+      <c r="F42">
+        <v>70</v>
+      </c>
+      <c r="G42" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B43" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43" t="s">
+        <v>33</v>
+      </c>
+      <c r="E43" t="s">
+        <v>69</v>
+      </c>
+      <c r="F43">
+        <v>80</v>
+      </c>
+      <c r="G43" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" t="s">
+        <v>25</v>
+      </c>
+      <c r="D44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E44" t="s">
+        <v>71</v>
+      </c>
+      <c r="F44">
+        <v>30</v>
+      </c>
+      <c r="G44" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" t="s">
+        <v>36</v>
+      </c>
+      <c r="E45" t="s">
+        <v>67</v>
+      </c>
+      <c r="F45">
+        <v>40</v>
+      </c>
+      <c r="G45" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B46" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" t="s">
+        <v>37</v>
+      </c>
+      <c r="E46" t="s">
+        <v>68</v>
+      </c>
+      <c r="F46">
+        <v>50</v>
+      </c>
+      <c r="G46" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="2">
+        <v>46135</v>
+      </c>
+      <c r="B47" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" t="s">
+        <v>38</v>
+      </c>
+      <c r="E47" t="s">
+        <v>69</v>
+      </c>
+      <c r="F47">
+        <v>60</v>
+      </c>
+      <c r="G47" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="2">
+        <v>46136</v>
+      </c>
+      <c r="B48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48" t="s">
+        <v>63</v>
+      </c>
+      <c r="E48" t="s">
+        <v>70</v>
+      </c>
+      <c r="F48">
+        <v>70</v>
+      </c>
+      <c r="G48" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="2">
+        <v>46082</v>
+      </c>
+      <c r="B49" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" t="s">
+        <v>39</v>
+      </c>
+      <c r="E49" t="s">
+        <v>71</v>
+      </c>
+      <c r="F49">
+        <v>80</v>
+      </c>
+      <c r="G49" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="2">
+        <v>46084</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="s">
+        <v>26</v>
+      </c>
+      <c r="D50" t="s">
+        <v>41</v>
+      </c>
+      <c r="E50" t="s">
+        <v>68</v>
+      </c>
+      <c r="F50">
+        <v>30</v>
+      </c>
+      <c r="G50" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" t="s">
+        <v>23</v>
+      </c>
+      <c r="D51" t="s">
+        <v>42</v>
+      </c>
+      <c r="E51" t="s">
+        <v>69</v>
+      </c>
+      <c r="F51">
+        <v>40</v>
+      </c>
+      <c r="G51" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="2">
+        <v>46086</v>
+      </c>
+      <c r="B52" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" t="s">
+        <v>24</v>
+      </c>
+      <c r="D52" t="s">
+        <v>43</v>
+      </c>
+      <c r="E52" t="s">
+        <v>70</v>
+      </c>
+      <c r="F52">
+        <v>50</v>
+      </c>
+      <c r="G52" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="2">
+        <v>46087</v>
+      </c>
+      <c r="B53" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" t="s">
+        <v>25</v>
+      </c>
+      <c r="D53" t="s">
+        <v>44</v>
+      </c>
+      <c r="E53" t="s">
+        <v>71</v>
+      </c>
+      <c r="F53">
+        <v>60</v>
+      </c>
+      <c r="G53" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="2">
+        <v>46088</v>
+      </c>
+      <c r="B54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" t="s">
+        <v>64</v>
+      </c>
+      <c r="E54" t="s">
+        <v>67</v>
+      </c>
+      <c r="F54">
+        <v>70</v>
+      </c>
+      <c r="G54" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="2">
+        <v>46089</v>
+      </c>
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" t="s">
+        <v>18</v>
+      </c>
+      <c r="D55" t="s">
+        <v>45</v>
+      </c>
+      <c r="E55" t="s">
+        <v>68</v>
+      </c>
+      <c r="F55">
+        <v>80</v>
+      </c>
+      <c r="G55" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="2">
+        <v>46091</v>
+      </c>
+      <c r="B56" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s">
+        <v>20</v>
+      </c>
+      <c r="D56" t="s">
+        <v>47</v>
+      </c>
+      <c r="E56" t="s">
+        <v>70</v>
+      </c>
+      <c r="F56">
+        <v>30</v>
+      </c>
+      <c r="G56" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="2">
+        <v>46092</v>
+      </c>
+      <c r="B57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57" t="s">
+        <v>48</v>
+      </c>
+      <c r="E57" t="s">
+        <v>71</v>
+      </c>
+      <c r="F57">
+        <v>40</v>
+      </c>
+      <c r="G57" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="2">
+        <v>46093</v>
+      </c>
+      <c r="B58" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" t="s">
+        <v>49</v>
+      </c>
+      <c r="E58" t="s">
+        <v>67</v>
+      </c>
+      <c r="F58">
+        <v>50</v>
+      </c>
+      <c r="G58" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="2">
+        <v>46094</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="s">
+        <v>26</v>
+      </c>
+      <c r="D59" t="s">
+        <v>50</v>
+      </c>
+      <c r="E59" t="s">
+        <v>68</v>
+      </c>
+      <c r="F59">
+        <v>60</v>
+      </c>
+      <c r="G59" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="2">
+        <v>46095</v>
+      </c>
+      <c r="B60" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" t="s">
+        <v>23</v>
+      </c>
+      <c r="D60" t="s">
+        <v>65</v>
+      </c>
+      <c r="E60" t="s">
+        <v>69</v>
+      </c>
+      <c r="F60">
+        <v>70</v>
+      </c>
+      <c r="G60" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="2">
+        <v>46096</v>
+      </c>
+      <c r="B61" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" t="s">
+        <v>51</v>
+      </c>
+      <c r="E61" t="s">
+        <v>70</v>
+      </c>
+      <c r="F61">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="2">
+        <v>46098</v>
+      </c>
+      <c r="B62" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" t="s">
+        <v>17</v>
+      </c>
+      <c r="D62" t="s">
+        <v>53</v>
+      </c>
+      <c r="E62" t="s">
+        <v>67</v>
+      </c>
+      <c r="F62">
+        <v>30</v>
+      </c>
+      <c r="G62" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="2">
+        <v>46099</v>
+      </c>
+      <c r="B63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" t="s">
+        <v>18</v>
+      </c>
+      <c r="D63" t="s">
+        <v>54</v>
+      </c>
+      <c r="E63" t="s">
+        <v>68</v>
+      </c>
+      <c r="F63">
+        <v>40</v>
+      </c>
+      <c r="G63" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="2">
+        <v>46100</v>
+      </c>
+      <c r="B64" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" t="s">
+        <v>55</v>
+      </c>
+      <c r="E64" t="s">
+        <v>69</v>
+      </c>
+      <c r="F64">
+        <v>50</v>
+      </c>
+      <c r="G64" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="2">
+        <v>46101</v>
+      </c>
+      <c r="B65" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" t="s">
+        <v>56</v>
+      </c>
+      <c r="E65" t="s">
+        <v>70</v>
+      </c>
+      <c r="F65">
+        <v>60</v>
+      </c>
+      <c r="G65" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="2">
+        <v>46102</v>
+      </c>
+      <c r="B66" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" t="s">
+        <v>21</v>
+      </c>
+      <c r="D66" t="s">
+        <v>66</v>
+      </c>
+      <c r="E66" t="s">
+        <v>71</v>
+      </c>
+      <c r="F66">
+        <v>70</v>
+      </c>
+      <c r="G66" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="2">
+        <v>46103</v>
+      </c>
+      <c r="B67" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" t="s">
+        <v>22</v>
+      </c>
+      <c r="D67" t="s">
+        <v>57</v>
+      </c>
+      <c r="E67" t="s">
+        <v>67</v>
+      </c>
+      <c r="F67">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="2">
+        <v>46105</v>
+      </c>
+      <c r="B68" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" t="s">
+        <v>23</v>
+      </c>
+      <c r="D68" t="s">
+        <v>59</v>
+      </c>
+      <c r="E68" t="s">
+        <v>69</v>
+      </c>
+      <c r="F68">
+        <v>30</v>
+      </c>
+      <c r="G68" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="2">
+        <v>46106</v>
+      </c>
+      <c r="B69" t="s">
+        <v>14</v>
+      </c>
+      <c r="C69" t="s">
+        <v>24</v>
+      </c>
+      <c r="D69" t="s">
+        <v>60</v>
+      </c>
+      <c r="E69" t="s">
+        <v>70</v>
+      </c>
+      <c r="F69">
+        <v>40</v>
+      </c>
+      <c r="G69" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="2">
+        <v>46107</v>
+      </c>
+      <c r="B70" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" t="s">
+        <v>25</v>
+      </c>
+      <c r="D70" t="s">
+        <v>61</v>
+      </c>
+      <c r="E70" t="s">
+        <v>71</v>
+      </c>
+      <c r="F70">
+        <v>50</v>
+      </c>
+      <c r="G70" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
